--- a/public/datos/3.4_Validacion_datos.xlsx
+++ b/public/datos/3.4_Validacion_datos.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Listas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Registro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas_Maestras" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Formulario_Captura" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Auditoria_Registros" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,153 +428,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Procesos</t>
+          <t>Sección</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Estados</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Responsables</t>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Direccionamiento estratégico</t>
+          <t>Código de Actividad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Laura Pimienta</t>
+          <t>3.4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gestión de la calidad</t>
+          <t>Título del Caso</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Por vencer</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Andrés Brito</t>
+          <t>Blindaje de captura y aseguramiento de calidad de datos SIG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Producción</t>
+          <t>Organización</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vencido</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Marelvis Ospino</t>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Comercial y ventas</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Kevin Fragozo</t>
+          <t>1. Situación Problema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>El personal registra novedades con constantes errores de digitación (nombres cortados, códigos inválidos, fechas incongruentes), arruinando búsquedas y reportes.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Logística y distribución</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yesenia Uriana</t>
+          <t>2. Misión del Aprendiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Blindar el formulario de captura con validaciones de lista, longitud, fecha y entero, configurar mensajes de alto restrictivos y corregir 8 registros corruptos.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Talento humano</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Camilo Iguarán</t>
+          <t>Requerimiento 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Listas Desplegables: En Proceso y Estado, configurar validación por lista referenciando Listas_Maestras.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compras</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Daniela Epiayú</t>
+          <t>Requerimiento 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Longitud de Código: En Código, restringir la longitud del texto a exactamente 12 caracteres (ej. PM-01-PR-01).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mantenimiento</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Rafael Mendoza</t>
+          <t>Requerimiento 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fechas y Versiones: Validar Fecha entre 01/01/2020 y 31/12/2026, y Versión número entero &gt;= 1.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Seguridad y salud en el trabajo</t>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mensajes y Alertas: Configurar Mensaje de Entrada orientativo y Mensaje de Error estilo 'Detener / Alto'.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gestión ambiental</t>
+          <t>Requerimiento 5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Auditoría con Círculos: En Auditoria_Registros, activar 'Rodear con un círculo datos no válidos' y corregir los 8 registros corruptos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>El estilo de alerta debe ser 'Detener' (no Información ni Advertencia) para bloquear físicamente el guardado de datos inválidos.</t>
         </is>
       </c>
     </row>
@@ -587,235 +590,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Código</t>
+          <t>Procesos Oficiales</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Documento</t>
+          <t>Estados Válidos</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Proceso</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
+          <t>Responsables Autorizados</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PM-01-PR-01</t>
+          <t>Direccionamiento estratégico</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control de producción</t>
+          <t>Vigente</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Produccion</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Por vencer</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Andrés Brito</t>
+          <t>Laura Pimienta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PE-02-MA-01</t>
+          <t>Gestión de la calidad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manual del SIG</t>
+          <t>Por vencer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gestión de la calidad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vijente</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Laura Pimienta</t>
+          <t>Andrés Brito</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PA-02-FO-01</t>
+          <t>Producción</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Orden de compra</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Compras</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Camilo Iguaran</t>
+          <t>Marelvis Ospino</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PM-02-PR-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Atención de PQRS</t>
+          <t>Comercial y ventas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Por vencer</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Marelvis Ospino</t>
+          <t>Kevin Fragozo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PA-04-IN-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Trabajo en alturas</t>
+          <t>Logística y distribución</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SST</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Vencido</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Daniela E.</t>
+          <t>Yesenia Uriana</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PM-03-PR-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Despacho y entrega</t>
+          <t>Talento humano</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Logística y distribución</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vencido</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Kevin Fragoso</t>
+          <t>Camilo Iguarán</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PA-01-PR-01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Selección y contratación</t>
+          <t>Compras</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Talento Humano</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Vencido</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Yesenia Uriana</t>
+          <t>Daniela Epiayú</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rafael Mendoza</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Seguridad y salud en el trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gestión ambiental</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código (12 caracteres)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proceso (Lista)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha Aprobación (2020-2026)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Versión (Entero &gt;=1)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Estado (Lista)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proceso</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha Aprobación</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PM-01-PR-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Control de producción</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>15/11/2024</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Andrés Brito</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PE-02-MA-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manual del SIG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gestión de la calidad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>01/03/2024</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vijente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Laura Pimienta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PA-02-FO-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Orden de compra</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Compras</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Camilo Iguarán</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PM-02-PR-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Atención de PQRS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>08/08/2024</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Marelvis Ospino</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PA-04-IN-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Trabajo en alturas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SST</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20/10/2023</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daniela Epiayú</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PM-03-PR-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Despacho y entrega</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Logística y distribución</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>22/05/2024</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Kevin Fragozo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PA-01-PR-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Selección y contratación</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Talento Humano</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>15/07/2024</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yesenia Uriana</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>PE-01-PO-01</t>
         </is>
       </c>
@@ -831,17 +1131,93 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>10/02/2030</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Vigente</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Rafael Mendoza</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PE-01-PL-1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Plan estratégico 2025-2028</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Direccionamiento estratégico</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>15/01/2025</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Por vencer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rafael Mendoza</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PM-01-FO-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Registro de temperatura</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Andrés Brito</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
